--- a/OUTPUT/reverse_C1F978_Acidobacterium_capsulatum_ATCC_51196.xlsx
+++ b/OUTPUT/reverse_C1F978_Acidobacterium_capsulatum_ATCC_51196.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.7272</v>
+        <v>0.727109156337465</v>
       </c>
     </row>
   </sheetData>
